--- a/exercisesLifeContingencies/test2_2021_22/makeham_comm.xlsx
+++ b/exercisesLifeContingencies/test2_2021_22/makeham_comm.xlsx
@@ -1,37 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="makeham" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="makeham" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>lx</t>
+  </si>
+  <si>
+    <t>dx</t>
+  </si>
+  <si>
+    <t>qx</t>
+  </si>
+  <si>
+    <t>px</t>
+  </si>
+  <si>
+    <t>exo</t>
+  </si>
+  <si>
+    <t>Dx</t>
+  </si>
+  <si>
+    <t>Nx</t>
+  </si>
+  <si>
+    <t>Sx</t>
+  </si>
+  <si>
+    <t>Cx</t>
+  </si>
+  <si>
+    <t>Mx</t>
+  </si>
+  <si>
+    <t>Rx</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +90,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,4865 +406,4837 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L127"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lx</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dx</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>qx</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>exo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dx</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Nx</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sx</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Cx</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mx</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>100000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30.09990444425847</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.0003009990444425847</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.9996990009555574</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>117.5179031967229</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>100000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>3841060.603717071</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>131210064.0282188</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>29.3657604334229</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>6315.595031291321</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>640815.1396141849</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>99969.90009555574</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>30.10023792762853</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.0003010930079839769</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.999698906992016</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>116.5531360788316</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>97531.60984932269</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>3741060.60371707</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>127369003.4245017</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>28.64983978834364</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>6286.229270857898</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>634499.5445828936</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>99939.79985762811</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>30.10141081574212</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.0003011954282340357</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.999698804571766</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>115.5880893908574</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>95124.14025711184</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>3643528.993867747</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>123627942.8207846</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>27.95215235135149</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>6257.579431069555</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>628213.3153120357</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:12">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>99909.69844681237</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>30.10349813338812</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.0003013070662946093</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.9996986929337054</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>114.622763841012</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>92776.08712287972</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>3548404.853610636</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>119984413.8269169</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>27.2722835446712</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>6229.627278718202</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>621955.7358809662</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>99879.59494867898</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>30.10658163232696</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.0003014287517665304</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.9996985712482335</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>113.6571602000485</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>90485.98344609409</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>3455628.766487756</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>116436008.9733063</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>26.60983126099812</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>6202.354995173531</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>615726.108602248</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>99849.48836704665</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>30.11075039430957</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.0003015613889139068</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.9996984386110861</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>112.6912793060805</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>88252.39840883081</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>3365142.783041662</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>112980380.2068185</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>25.96440569673218</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>6175.745163912534</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>609523.7536070744</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>99819.37761665235</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>30.11610148828679</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.0003017059633846353</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.9996982940366154</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>111.7251220697629</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>86073.93648096749</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>3276890.384632831</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>109615237.4237768</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>25.33562919833971</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>6149.780758215802</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>603348.0084431618</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:12">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>99789.26151516406</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>30.12274068633165</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.0003018635495338762</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.9996981364504661</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>110.7586894798574</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>83949.23654735531</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>3190816.448151864</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>106338347.039144</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>24.72313612179871</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>6124.445129017462</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>597198.227684946</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>99759.13877447773</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>30.13078324387944</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.0003020353184082225</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.9996979646815918</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>109.7919826092129</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>81876.97105641996</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>3106867.211604508</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>103147530.5909922</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>24.12657270568451</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>6099.721992895664</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>591073.7825559286</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>99729.00799123386</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>30.14035474980654</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.000302222546447628</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.9996977774535524</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>108.8250026211896</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>79855.84518965527</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>3024990.240548088</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>100040663.3793877</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>23.5455969579953</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6075.595420189979</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>584974.0605630329</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>99698.86763648405</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>30.15159205270328</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.0003024266249707086</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.9996975733750293</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>107.8577507765566</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>77884.59605148618</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>2945134.395358433</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>97015673.13883956</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>22.9798785571297</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6052.049823231984</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>578898.465142843</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>99668.71604443135</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>30.16464427010727</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.0003026490705133611</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.9996973509294866</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>106.8902284408988</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>75961.99187899037</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>2867249.799306947</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>94070538.74348113</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>22.42909876733651</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>6029.069944674853</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>572846.415319611</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>99638.55140016125</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>30.17967388821574</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.0003028915360984152</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.9996971084639016</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>105.9224370925666</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>74086.83127097938</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>2791287.807427957</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>91203288.94417417</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>21.89295036910346</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>6006.640845907517</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>566817.3453749361</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:12">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>99608.37172627304</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>30.1968579600901</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.0003031558235192522</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.9996968441764807</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>104.9543783312076</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>72257.94243595225</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>2717200.976156978</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>88412001.13674623</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>21.37113760485642</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>5984.747895538414</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>560810.7045290285</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:12">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>99578.17486831294</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>30.21638941113465</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.0003034438967283171</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.9996965561032717</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>103.98605388692</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>70474.18245844613</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>2644943.033721025</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>85694800.16058925</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>20.86337614042273</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>5963.376757933557</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>554825.9566334902</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:12">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>99547.95847890181</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>30.23847846161812</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.0003037578964316667</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.9996962421035683</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>103.0174656300702</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>68734.43658331923</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>2574468.851262579</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>83049857.12686822</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>20.36939304289253</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>5942.513381793135</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>548862.5798755565</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:12">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>99517.7200004402</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>30.26335417650242</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.0003041001559960232</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.999695899844004</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>102.0486155818213</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>67037.61751751245</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>2505734.41467926</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>80475388.27560565</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>19.88892677529491</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>5922.143988750242</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>542920.0664937635</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:12">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>99487.4566462637</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>30.29126615408787</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.000304473218787682</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.9996955267812123</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>101.0795059254193</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>65382.66474884662</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>2438696.797161747</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>77969653.86092637</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>19.4217272087778</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>5902.255061974947</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>536997.9225050133</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:12">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>99457.16538010961</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>30.32248636586902</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.0003048798570719491</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.9996951201429281</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>100.1101390182888</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>63768.54388142208</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>2373314.132412901</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>75530957.06376463</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>18.967555652931</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>5882.833334766169</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>531095.6674430383</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:12">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>99426.84289374374</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>30.35731116109752</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.0003053230926133299</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.9996946769073867</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>99.14051740499384</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>62194.24598719788</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>2309545.588531479</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>73157642.93135172</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>18.5261849049419</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>5863.865779113238</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>525212.8341082721</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:12">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>99396.48558258264</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>30.39606345078719</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.0003058062191296784</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.9996941937808703</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>98.17064383111851</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>60658.78697333689</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>2247351.342544281</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>70848097.34282026</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>18.09739931835</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>5845.339594208296</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>519348.9683291589</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:12">
+      <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>99366.08951913186</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>30.43909508714066</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.0003063328267666199</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.9996936671732334</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>97.20052125813147</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>59161.20696491278</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>2186692.555570944</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>68600746.00027595</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>17.68099489218222</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>5827.242194889946</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>513503.6287349506</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:12">
+      <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>99335.65042404471</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>30.4867894559334</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.0003069068287748777</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.9996930931712251</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>96.23015287929654</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>57700.5697025837</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>2127531.348606031</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>66414053.44470502</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>17.27677938138903</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>5809.561199997765</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>507676.3865400606</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:12">
+      <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>99305.16363458878</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>30.53956430083946</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.000307532490588458</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.9996924675094115</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>95.25954213669864</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>56275.96195484662</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>2069830.778903448</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>64286522.09609898</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>16.88457242949784</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>5792.284420616375</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>501866.8253400629</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:12">
+      <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>99274.62407028794</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>30.59787480034333</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.0003082144615191851</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.9996917855384808</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>94.28869273945642</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>54886.49294449404</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>2013554.816948601</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>62216691.31719555</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>16.50420572445247</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>5775.399848186877</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>496074.5409194466</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:12">
+      <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>99244.0261954876</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>30.66221691986225</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.0003089578093039558</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.999691042190696</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>93.31760868319773</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>53531.29378890389</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>1958668.324004107</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>60203136.50024693</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>16.13552317875727</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>5758.895642462425</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>490299.1410712596</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:12">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>99213.36397856774</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>30.733131063428</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>0.0003097680577595074</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.9996902319422405</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>92.34629427087766</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>52209.51695380064</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>1905137.030215203</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>58244468.17624284</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>15.77838113496673</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>5742.760119283667</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>484540.2454287972</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:12">
+      <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>99182.6308475043</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>30.81120605201341</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>0.0003106512278282514</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.9996893487721717</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>91.37475413502322</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>50920.33572013396</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>1852927.513261402</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>56339331.14602763</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>15.43264859793794</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>5726.981738148701</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>478797.4853095136</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:12">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>99151.8196414523</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>30.8970834569968</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>0.0003116138823142656</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.9996883861176857</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>90.40299326149317</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>49662.94366372788</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>1802007.177541269</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>54486403.63276623</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>15.09820749483795</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>5711.549089550763</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>473070.5035713649</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:12">
+      <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>99120.92255799531</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>30.99146232103877</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>0.0003126631746481756</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.9996873368253518</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>89.43101701484561</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>48436.55414736164</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>1752344.233877541</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>52684396.45522495</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>14.77495296461692</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>5696.450882055925</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>467358.9544818142</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:12">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>99089.93109567427</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>31.09510430026764</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>0.0003138069020377499</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>0.9996861930979623</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>88.45883116541077</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>47240.39982494919</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>1703907.679730179</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>50932052.22134742</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>14.4627936781385</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>5681.675929091307</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>461662.5035997581</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:12">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>99058.835991374</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>31.2088392655148</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>0.0003150535634017793</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>0.9996849464365982</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>87.48644191817047</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>46073.7321574918</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>1656667.27990523</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>49228144.54161724</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>14.16165219067019</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>5667.213135413169</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>455980.8276706669</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:12">
+      <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>99027.62715210849</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>31.33357140339779</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>0.0003164124225178977</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>0.9996835875774821</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>86.51385594355079</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>44935.82094048426</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>1610593.547747738</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>47571477.26171201</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>13.87146532839912</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>5653.0514832225</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>450313.6145352537</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:12">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>98996.29358070508</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>31.47028586130405</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>0.0003178935768504143</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>0.9996821064231496</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>85.54108041023946</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>43825.95384246112</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>1565657.726807254</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>45960883.71396428</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>13.59218461059622</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>5639.1800178941</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>444660.5630520312</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:12">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>98964.82329484378</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>31.62005598489995</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>0.0003195080325733013</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>0.9996804919674267</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>84.56812302014228</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>42743.43595437587</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>1521831.772964793</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>44395225.98715702</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>13.32377670946882</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>5625.587833283504</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>439021.3830341371</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:12">
+      <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>98933.20323885889</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>31.78405120020602</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>0.0003212677863413393</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>0.9996787322136587</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>83.59499204560002</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>41687.5893495109</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>1479088.337010417</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>42873394.21419223</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37">
         <v>13.06622394948699</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>5612.264056574035</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>433395.7952008536</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:12">
+      <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>98901.41918765868</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>31.96354559760349</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>0.0003231859144200433</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>0.99967681408558</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>82.62169636898942</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>40657.75265362213</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>1437400.747660906</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>41394305.87718181</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>12.81952484841445</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38">
         <v>5599.197832624548</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>427783.5311442795</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:12">
+      <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>98869.45564206108</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>32.15992727951229</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>0.0003252766698336185</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>0.9996747233301664</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>81.64824552483736</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>39653.28062502683</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>1396742.995007284</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>39956905.1295209</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>12.58369470213334</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>5586.378307776134</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>422184.333311655</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:12">
+      <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>98837.29571478156</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>32.37470853926046</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>0.0003275555882537029</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>0.9996724444117463</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>80.6746497445812</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>38673.54374434844</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>1357089.714382257</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>38560162.13451362</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>12.35876621564426</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>5573.794613074</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>416597.9550038789</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:12">
+      <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>98804.92100624231</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>32.60953694427821</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>0.0003300396034142672</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>0.9996699603965857</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>79.70092000411164</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>37717.9278136365</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>1318416.170637908</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>37203072.42013136</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>12.1447901826542</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>5561.435846858356</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41">
         <v>411024.1603908049</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:12">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>98772.31146929803</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>32.86620740305097</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>0.0003327471729085429</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>0.9996672528270915</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>78.72706807423855</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>36785.83356458467</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>1280698.242824272</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>35884656.24949345</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>11.94183621629243</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>5549.291056675702</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>405462.7245439465</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:12">
+      <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>98739.44526189497</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>33.14667530243699</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>0.0003356984153042308</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>0.9996643015846958</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>77.75310657422241</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>35876.67627557362</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>1243912.409259687</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>34603958.00666919</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>11.74999353374923</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>5537.349220459409</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>399913.4334872708</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:12">
+      <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>98706.29858659253</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>33.4530708087702</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>0.0003389152595912881</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>0.9996610847404087</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>76.77904902851752</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>34989.88539726978</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>1208035.732984113</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>33360045.59740949</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44">
         <v>11.56937179754645</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>5525.59922692566</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>394376.0842668114</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:12">
+      <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>98672.84551578376</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>33.78771443468255</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>0.0003424216080732956</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>0.9996575783919267</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>75.80490992687348</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>34124.90418651445</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>1173045.847586844</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>32152009.86442538</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45">
         <v>11.40010201648138</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45">
         <v>5514.029855128114</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>388850.4850398857</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:12">
+      <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>98639.05780134907</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>34.1531339818882</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>0.0003462435139097719</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>0.9996537564860902</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>74.83070478794426</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>33281.18934824152</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>1138920.943400329</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>30978964.01683854</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>11.24233750929914</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>5502.629753111632</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46">
         <v>383336.4551847577</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:12">
+      <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>98604.90466736718</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>34.55208297972841</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>0.0003504093746278247</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>0.9996495906253722</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>73.85645022655257</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>32458.21068516535</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>1105639.754052088</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>29840043.07343821</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>11.09625493436778</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>5491.387415602334</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>377833.8254316461</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:12">
+      <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>98570.35258438745</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>34.98756074896936</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>0.0003549501430363255</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>0.9996450498569637</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>72.88216402475733</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>31655.45075498305</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>1073181.543366922</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>28734403.31938612</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>10.96205538864448</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>5480.291160667965</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48">
         <v>372342.4380160437</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:12">
+      <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>98535.36502363849</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>35.46283423144114</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>0.0003598995571075791</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>0.9996401004428924</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>71.90786520686946</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>30872.40453483873</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>1041526.092611939</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>27661221.7760192</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>10.83996557944827</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>5469.329105279321</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>366862.1468553758</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:12">
+      <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>98499.90218940705</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>35.98146173777501</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>0.0003652943905323447</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>0.9996347056094677</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>70.93357411855733</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>30108.5790927998</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>1010653.688077101</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>26619695.68340726</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50">
         <v>10.73023907268215</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50">
         <v>5458.489139699873</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>361392.8177500964</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:12">
+      <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>98463.92072766928</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>36.54731877752113</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>0.0003711747258023923</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>0.9996288252741976</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>69.95931251017805</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>29363.49326609786</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>980545.1089843006</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>25609041.99533016</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>10.63315762111636</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>5447.75890062719</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>355934.3286103965</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:12">
+      <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>98427.37340889176</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>37.16462614973894</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>0.0003775842518457528</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>0.9996224157481542</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>68.98510362446321</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>28636.67734588899</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>951181.6157182029</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>24628496.88634586</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52">
         <v>10.54903257658119</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>5437.125743006074</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52">
         <v>350486.5697097693</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:12">
+      <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>98390.20878274202</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>37.83798048646668</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>0.0003845705884212292</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>0.9996154294115788</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>68.01097228867805</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>27927.67276829073</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>922544.9383723139</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>23677315.27062766</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>10.47820638998742</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>5426.576710429493</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>345049.4439667633</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:12">
+      <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>98352.37080225555</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>38.57238745631022</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>0.0003921856396716938</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>0.9996078143603283</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>67.03694501136124</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>27236.03181145463</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>894617.2656040231</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>22754770.33225534</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>10.42105420301847</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>5416.098504039506</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>339622.8672563338</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:12">
+      <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>98313.79841479924</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>39.37329785228558</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>0.000400485979456966</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>0.999599514020543</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>66.06305008373684</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>26561.31729843565</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>867381.2337925686</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>21860153.06665132</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55">
         <v>10.37798553554269</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>5405.677449836487</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55">
         <v>334206.7687522942</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:12">
+      <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>98274.42511694695</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>40.24664680490676</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>0.0004095332713166533</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>0.9995904667286833</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>65.08931768587217</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>25903.10230562119</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>840819.916494133</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>20992771.83285875</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>10.34944607265462</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>5395.299464300944</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56">
         <v>328801.0913024577</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:12">
+      <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>98234.17847014204</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>41.19889638012127</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>0.0004193947261710296</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>0.999580605273829</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>64.1157799976333</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>25260.9698764846</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>814916.8141885116</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>20151951.91636462</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57">
         <v>10.33591955528087</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>5384.95001822829</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>323405.7918381569</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:12">
+      <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>98192.97957376191</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>42.23708184114783</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>0.0004301436011463489</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>0.9995698563988537</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>63.14247131446308</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>24634.5127404297</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>789655.844312027</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>19337035.10217611</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>10.33792977819907</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58">
         <v>5374.614098673009</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58">
         <v>318020.8418199286</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:12">
+      <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>98150.74249192077</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>43.36886187338192</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>0.0004418597432103155</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>0.9995581402567897</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>62.16942816797703</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>24023.33303649468</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>765021.3315715974</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>18547379.25786408</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>10.35604269908432</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K59">
         <v>5364.276168894809</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59">
         <v>312646.2277212555</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:12">
+      <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>98107.37363004738</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>44.60257309342774</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>0.0004546301816377163</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>0.9995453698183623</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>61.19668945133493</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>23427.04204168597</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>740997.9985351027</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>17782357.92629249</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>10.39086866209377</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>5353.920126195726</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>307281.9515523607</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:12">
+      <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>98062.77105695395</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>45.94728918522869</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>0.0004685497736806044</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>0.9995314502263194</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>60.22429654930496</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>22845.25990371446</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>717570.9564934167</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>17041359.92775738</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>10.44306473908292</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>5343.529257533632</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>301928.031426165</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:12">
+      <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>98016.82376776871</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>47.41288502967186</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>0.0004837219082104438</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>0.9995162780917896</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>59.2522934728886</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>22277.61537790918</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>694725.6965897022</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>16323788.97126396</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62">
         <v>10.51333719120054</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62">
         <v>5333.086192794548</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>296584.5021686314</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:12">
+      <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>97969.41088273904</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>49.01010621771204</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>0.0005002592725230626</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>0.9994997407274769</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>58.28072699831821</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>21723.74556808605</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>672448.081211793</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>15629063.27467426</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>10.60244405304081</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>5322.572855603348</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>291251.4159758368</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:12">
+      <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>97920.40077652133</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>50.75064436144295</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>0.0005182846879606684</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>0.9994817153120393</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>57.30964681017628</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>21183.29567115286</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>650724.3356437071</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>14956615.19346247</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>10.71119784088004</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>5311.970411550307</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>285928.8431202335</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:12">
+      <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>97869.65013215989</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>52.64721864196064</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>0.0005379320205075588</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>0.9994620679794924</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>56.33910564831118</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>20655.91872523509</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>629541.0399725541</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>14305890.85781876</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>10.84046838566403</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K65">
         <v>5301.259213709427</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65">
         <v>280616.8727086831</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:12">
+      <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>97817.00291351794</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>54.71366405712225</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>0.0005593471730624966</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>0.9994406528269375</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>55.36915945814255</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>20141.27536111198</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>608885.121247319</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>13676349.81784621</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66">
         <v>10.99118579035249</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66">
         <v>5290.418745323763</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>275315.6134949737</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:12">
+      <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>97762.28924946081</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>56.96502685631424</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>0.0005826891666883549</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>0.9994173108333116</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>54.39986754385472</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>19639.03355675792</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>588743.8458862071</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>13067464.69659889</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>11.16434351000187</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>5279.427559533411</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>270025.19474965</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:12">
+      <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>97705.3242226045</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>59.41766767169015</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>0.0006081313187837889</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>0.9993918686812162</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>53.43129272387042</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>19148.86839479041</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>569104.8123294492</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>12478720.85071268</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68">
         <v>11.36100155135718</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K68">
         <v>5268.26321602341</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>264745.7671901166</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:12">
+      <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>97645.90655493281</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>62.0893728764099</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>0.0006358625268277907</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>0.9993641374731722</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>52.46350148787764</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>18670.46182263441</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>549955.9439346588</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>11909616.03838323</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69">
         <v>11.58228978690938</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>5256.902214472051</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>259477.5039740931</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:12">
+      <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>97583.8171820564</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>64.99947471843606</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>0.0006660886671113753</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>0.9993339113328886</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>51.49656415454732</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>18203.50241522228</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>531285.4821120243</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>11359660.09444857</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>11.82941137611132</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70">
         <v>5245.319924685142</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70">
         <v>254220.6017596211</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:12">
+      <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>97518.81770733796</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>68.16898079278893</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>0.0006990341187007587</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>0.9993009658812992</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>50.53055502892848</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71">
         <v>17747.68514006026</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71">
         <v>513081.979696802</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>10828374.61233655</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71">
         <v>12.10364628376641</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>5233.490513309031</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>248975.2818349359</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:12">
+      <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>97450.64872654517</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>71.62071342491795</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>0.0007349434237825525</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>0.9992650565762174</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>49.56555255833837</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>17302.71112450673</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>495334.2945567418</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>10315292.63263975</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>12.40635488250287</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>5221.386867025265</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72">
         <v>243741.7913216269</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:12">
+      <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>97379.02801312026</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>75.37945954008725</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>0.0007740830965157208</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>0.9992259169034843</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>48.60163948537508</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73">
         <v>16868.28742512406</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>478031.5834322351</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>9819958.338083003</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>12.7389816223973</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73">
         <v>5208.980512142762</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>238520.4044546017</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:12">
+      <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>97303.64855358018</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>79.47213158876346</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>0.000816743593586855</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>0.9991832564064131</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>47.63890299646946</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>16444.12679898645</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>461163.296007111</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>9341926.754650768</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>13.10305874653864</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>5196.241530520365</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>233311.4239424589</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:12">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>97224.17642199142</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>83.92794008091059</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>0.0008632414608135131</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>0.9991367585391865</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>46.67743486415662</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>16029.94747685</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>444719.1692081246</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>8880763.458643658</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75">
         <v>13.50021002602915</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>5183.138471773826</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>228115.1824119385</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:12">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>97140.2484819105</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>88.77857825241371</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>0.0009139216713960341</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>0.999086078328604</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>45.71733158098549</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>15625.47293812031</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>428689.2217312746</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>8436044.289435532</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>13.9321544819126</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>5169.638261747798</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>222932.0439401647</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:12">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>97051.46990365809</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>94.05841934004103</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>0.0009691601727764843</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>0.9990308398272235</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>44.75869448269233</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>15230.43168758669</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>413063.7487931543</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>8007355.067704258</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>14.40071005444093</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>5155.706107265883</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>217762.4056784169</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:12">
+      <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>96957.41148431804</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>99.80472687356804</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>0.001029366660533326</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>0.9989706333394667</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>43.80162985793974</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>14844.55703393257</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>397833.3171055676</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>7594291.318911104</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>14.90779717182017</v>
       </c>
-      <c r="K78" t="n">
+      <c r="K78">
         <v>5141.305397211443</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78">
         <v>212606.6995711511</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:12">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>96857.60675744448</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>106.0578783009382</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>0.001094987599337793</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>0.9989050124006622</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>42.8462490415623</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>14467.58687007947</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>382988.760071635</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>7196458.001805536</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>15.45544216105298</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>5126.397600039623</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79">
         <v>207465.3941739396</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:12">
+      <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>96751.54887914353</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>112.8616021377554</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>0.00116650951271835</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>0.9988334904872816</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>41.89266848785934</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>14099.26345547745</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>368521.1732015556</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>6813469.241733901</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80">
         <v>16.04578043232843</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>5110.94215787857</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80">
         <v>202338.9965739</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:12">
+      <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>96638.68727700578</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>120.2632286711688</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>0.001244462565250348</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>0.9987555374347497</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>40.94100982003106</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81">
         <v>13739.33320052129</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81">
         <v>354421.9097460781</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>6444948.068532346</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81">
         <v>16.68105935565854</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81">
         <v>5094.896377446242</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81">
         <v>197228.0544160214</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:12">
+      <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>96518.42404833461</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>128.3139540409784</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>0.001329424462802264</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>0.9986705755371977</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>39.99139985136067</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82">
         <v>13387.54645334804</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82">
         <v>340682.5765455568</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>6090526.158786267</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82">
         <v>17.36364073364154</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82">
         <v>5078.215318090583</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82">
         <v>192133.1580385751</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:12">
+      <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>96390.11009429363</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>137.0691172596829</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>0.001422024698650048</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>0.99857797530135</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>39.043970573197</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83">
         <v>13043.65728936201</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83">
         <v>327295.0300922088</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>5749843.582240711</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J83">
         <v>18.09600275726782</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>5060.851677356942</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83">
         <v>187054.9427204846</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:12">
+      <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>96253.04097703395</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>146.5884894068292</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>0.001522949175619348</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>0.9984770508243807</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>38.09885910418286</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84">
         <v>12707.42330393737</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84">
         <v>314251.3728028468</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>5422548.552148502</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84">
         <v>18.88074131217319</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84">
         <v>5042.755674599674</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84">
         <v>181994.0910431276</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:12">
+      <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>96106.45248762712</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>156.936573829876</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>0.001632945236950456</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>0.9983670547630495</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>37.15620759449585</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85">
         <v>12378.60540887063</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85">
         <v>301543.9494989094</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85">
         <v>5108297.179345655</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J85">
         <v>19.72057048049215</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K85">
         <v>5023.8749332875</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85">
         <v>176951.3353685279</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:12">
+      <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>95949.51591379724</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>168.1829156891081</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>0.001752827141308422</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>0.9982471728586916</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>36.21616307811336</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86">
         <v>12056.96763329574</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86">
         <v>289165.3440900387</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>4806753.229846746</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86">
         <v>20.61832205806628</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>5004.154362807009</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86">
         <v>171927.4604352405</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:12">
+      <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>95781.33299810813</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>180.4024185814082</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>0.00188348202029065</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>0.9981165179797094</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>35.27887726526946</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87">
         <v>11742.27692993777</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87">
         <v>277108.376456743</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>4517587.885756708</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J87">
         <v>21.57694387786487</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87">
         <v>4983.536040748942</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87">
         <v>166923.3060724335</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:12">
+      <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>95600.93057952673</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>193.6756652490951</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>0.002025876359937562</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>0.9979741236400624</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>34.34450626632799</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88">
         <v>11434.30298776874</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88">
         <v>265366.0995268053</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>4240479.509299965</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J88">
         <v>22.59949669783818</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K88">
         <v>4961.959096871077</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88">
         <v>161939.7700316845</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:12">
+      <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>95407.25491427763</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>208.0892385026127</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>0.002181063051123089</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>0.9978189369488769</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>33.41321023723721</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89">
         <v>11132.81805234484</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89">
         <v>253931.7965390366</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89">
         <v>3975113.40977316</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J89">
         <v>23.68914937448336</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>4939.359600173239</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89">
         <v>156977.8109348134</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:12">
+      <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>95199.16567577502</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>223.7360374372093</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>0.002350189057320096</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>0.9976498109426799</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>32.48515293554055</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90">
         <v>10837.59675535219</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90">
         <v>242798.9784866917</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>3721181.613234124</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J90">
         <v>24.84917200202585</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>4915.670450798756</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90">
         <v>152038.4513346402</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:12">
+      <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>94975.42963833781</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>240.7155827744497</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>0.002534503752087081</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>0.9974654962479129</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>31.56050117457324</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91">
         <v>10548.41595517085</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91">
         <v>231961.3817313395</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>3478382.634747432</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J91">
         <v>26.08292665068852</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91">
         <v>4890.82127879673</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91">
         <v>147122.7808838414</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:12">
+      <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>94734.71405556337</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>259.1343036817423</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>0.002735367982741321</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>0.9972646320172587</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>30.63942416194953</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92">
         <v>10265.05459058916</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92">
         <v>221412.9657761687</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>3246421.253016092</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92">
         <v>27.39385528603846</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>4864.738352146042</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92">
         <v>142231.9596050447</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:12">
+      <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>94475.57975188163</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>279.1057966810795</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>0.002954263921048028</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>0.997045736078952</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>29.72209270671091</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93">
         <v>9987.293550166803</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93">
         <v>211147.9111855795</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93">
         <v>3025008.287239923</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93">
         <v>28.78546439431557</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>4837.344496860003</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93">
         <v>137367.2212528987</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:12">
+      <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>94196.47395520055</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>300.7510452177306</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>0.003192805766389584</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>0.9968071942336104</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>28.8086782775198</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94">
         <v>9714.915560158664</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94">
         <v>201160.6176354127</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>2813860.376054344</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94">
         <v>30.26130577606096</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94">
         <v>4808.559032465688</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94">
         <v>132529.8767560387</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:12">
+      <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>93895.72290998281</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>324.198586080553</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>0.003452751371767593</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>0.9965472486282324</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>27.89935189200231</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95">
         <v>9447.705094378734</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95">
         <v>191445.702075254</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95">
         <v>2612699.758418931</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J95">
         <v>31.82495290211888</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95">
         <v>4778.297726689627</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95">
         <v>127721.317723573</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:12">
+      <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>93571.52432390225</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>349.5846061085199</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>0.003736014868138904</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>0.9962639851318611</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>26.99428281470656</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96">
         <v>9185.448309906402</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96">
         <v>181997.9969808753</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96">
         <v>2421254.056343677</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96">
         <v>33.47997215251872</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96">
         <v>4746.472773787507</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96">
         <v>122943.0199968833</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:12">
+      <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>93221.93971779374</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>377.0529494411927</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>0.004044680367975895</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>0.9959553196320241</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>26.09363703807871</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97">
         <v>8927.933013122021</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97">
         <v>172812.5486709689</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97">
         <v>2239256.059362802</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97">
         <v>35.22988818027173</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97">
         <v>4712.99280163499</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97">
         <v>118196.5472230958</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:12">
+      <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>92844.88676835255</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>406.7550119344688</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>0.004381016834554607</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>0.9956189831654454</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>25.19757551727801</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98">
         <v>8674.948661207067</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98">
         <v>163884.6156578469</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98">
         <v>2066443.510691833</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J98">
         <v>37.07814255965377</v>
       </c>
-      <c r="K98" t="n">
+      <c r="K98">
         <v>4677.762913454717</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98">
         <v>113483.5544214608</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:12">
+      <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>92438.13175641808</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>438.8494952313445</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>0.004747494209291769</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>0.9952525057907082</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>24.30625212544177</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99">
         <v>8426.286404959437</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99">
         <v>155209.6669966398</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99">
         <v>1902558.895033986</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J99">
         <v>39.02804479354039</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99">
         <v>4640.684770895063</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99">
         <v>108805.7915080061</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:12">
+      <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>91999.28226118673</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>473.5019883200846</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>0.005146800895422299</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>0.9948531991045777</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>23.41981129103331</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100">
         <v>8181.73917955713</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100">
         <v>146783.3805916804</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100">
         <v>1747349.228037346</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100">
         <v>41.08271466873789</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100">
         <v>4601.656726101523</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100">
         <v>104165.1067371111</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:12">
+      <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>91525.78027286664</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>510.8843392123812</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>0.00558186270239136</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>0.9944181372976086</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>22.53838527298539</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101">
         <v>7941.101850752852</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101">
         <v>138601.6414121232</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101">
         <v>1600565.847445666</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J101">
         <v>43.24501486498377</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K101">
         <v>4560.574011432785</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101">
         <v>99563.45001100954</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:12">
+      <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>91014.89593365426</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>551.1737736317946</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>0.006055863361460911</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>0.9939441366385391</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>21.6620910222696</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102">
         <v>7704.171424893898</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102">
         <v>130660.5395613704</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102">
         <v>1461964.206033543</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J102">
         <v>45.51747264627226</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102">
         <v>4517.328996567801</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102">
         <v>95002.87599957675</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:12">
+      <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>90463.72216002247</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>594.551711342917</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>0.006572266729100606</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>0.9934277332708994</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>20.79102657000277</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103">
         <v>7470.747332128263</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103">
         <v>122956.3681364765</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103">
         <v>1331303.666472172</v>
       </c>
-      <c r="J103" t="n">
+      <c r="J103">
         <v>47.90218939752558</v>
       </c>
-      <c r="K103" t="n">
+      <c r="K103">
         <v>4471.811523921529</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103">
         <v>90485.54700300895</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:12">
+      <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>89869.17044867955</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>641.2022240383039</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>0.007134840800655518</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>0.9928651591993445</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>19.92526687189795</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104">
         <v>7240.631793166634</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104">
         <v>115485.6208043482</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104">
         <v>1208347.298335696</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J104">
         <v>50.40073672235007</v>
       </c>
-      <c r="K104" t="n">
+      <c r="K104">
         <v>4423.909334524003</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104">
         <v>86013.73547908742</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:12">
+      <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>89227.96822464124</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>691.3100716425827</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>0.00774768366239309</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>0.9922523163376069</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>19.06485902633814</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105">
         <v>7013.630281001195</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105">
         <v>108244.9890111816</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105">
         <v>1092861.677531347</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J105">
         <v>53.01403779724724</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105">
         <v>4373.508597801654</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105">
         <v>81589.82614456341</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:12">
+      <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>88536.65815299866</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>745.0582466708354</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>0.00841525151517819</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>0.9915847484848218</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>18.20981676803824</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106">
         <v>6789.552090008798</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106">
         <v>101231.3587301804</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106">
         <v>984616.6885201656</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J106">
         <v>55.74223269544174</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106">
         <v>4320.494560004407</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106">
         <v>77216.31754676175</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:12">
+      <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>87791.59990632783</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>802.6249491525476</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>0.009142388907468768</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>0.9908576110925312</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>17.36011412045162</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107">
         <v>6568.211025849728</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H107">
         <v>94441.80664017156</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I107">
         <v>883385.3297899853</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J107">
         <v>58.58452646306596</v>
       </c>
-      <c r="K107" t="n">
+      <c r="K107">
         <v>4264.752327308965</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L107">
         <v>72895.82298675735</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:12">
+      <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>86988.97495717528</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>864.179907978371</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>0.009934361318820084</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108">
         <v>0.9900656386811799</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>16.51567806686317</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108">
         <v>6349.426230463498</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H108">
         <v>87873.59561432185</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I108">
         <v>788943.5231498138</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J108">
         <v>61.53901886889581</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K108">
         <v>4206.167800845898</v>
       </c>
-      <c r="L108" t="n">
+      <c r="L108">
         <v>68631.07065944839</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:12">
+      <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>86124.79504919691</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>929.879958855374</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>0.01079689023729113</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>0.9892031097627089</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>15.67638007132225</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109">
         <v>6133.023157193055</v>
       </c>
-      <c r="H109" t="n">
+      <c r="H109">
         <v>81524.16938385836</v>
       </c>
-      <c r="I109" t="n">
+      <c r="I109">
         <v>701069.9275354919</v>
       </c>
-      <c r="J109" t="n">
+      <c r="J109">
         <v>64.60251497656404</v>
       </c>
-      <c r="K109" t="n">
+      <c r="K109">
         <v>4144.628781977002</v>
       </c>
-      <c r="L109" t="n">
+      <c r="L109">
         <v>64424.9028586025</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:12">
+      <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>85194.91509034153</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110">
         <v>999.8637850525954</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>0.01173619087468225</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>0.9882638091253177</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>14.84202624470396</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110">
         <v>5918.834711553245</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H110">
         <v>75391.1462266653</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I110">
         <v>619545.7581516335</v>
       </c>
-      <c r="J110" t="n">
+      <c r="J110">
         <v>67.77031602974024</v>
       </c>
-      <c r="K110" t="n">
+      <c r="K110">
         <v>4080.026267000439</v>
       </c>
-      <c r="L110" t="n">
+      <c r="L110">
         <v>60280.27407662549</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:12">
+      <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>84195.05130528893</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111">
         <v>1074.245725675057</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>0.01275901266191848</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>0.9872409873380815</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>14.0123459062997</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111">
         <v>5706.702573290499</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H111">
         <v>69472.31151511204</v>
       </c>
-      <c r="I111" t="n">
+      <c r="I111">
         <v>544154.6119249683</v>
       </c>
-      <c r="J111" t="n">
+      <c r="J111">
         <v>71.03599062479634</v>
       </c>
-      <c r="K111" t="n">
+      <c r="K111">
         <v>4012.255950970698</v>
       </c>
-      <c r="L111" t="n">
+      <c r="L111">
         <v>56200.24780962506</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:12">
+      <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>83120.80557961387</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>1153.108558462517</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>0.01387268266256225</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>0.9861273173374377</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>13.18697823490222</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112">
         <v>5496.478715024471</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H112">
         <v>63765.60894182156</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I112">
         <v>474682.3004098563</v>
       </c>
-      <c r="J112" t="n">
+      <c r="J112">
         <v>74.39112680493896</v>
       </c>
-      <c r="K112" t="n">
+      <c r="K112">
         <v>3941.219960345902</v>
       </c>
-      <c r="L112" t="n">
+      <c r="L112">
         <v>52187.99185865436</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:12">
+      <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>81967.69702115135</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>1236.495171498737</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>0.0150851520347054</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>0.9849148479652946</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>12.36545663206786</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113">
         <v>5288.027131755522</v>
       </c>
-      <c r="H113" t="n">
+      <c r="H113">
         <v>58269.13022679708</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I113">
         <v>410916.6914680346</v>
       </c>
-      <c r="J113" t="n">
+      <c r="J113">
         <v>77.8250665816382</v>
       </c>
-      <c r="K113" t="n">
+      <c r="K113">
         <v>3866.828833540963</v>
       </c>
-      <c r="L113" t="n">
+      <c r="L113">
         <v>48246.77189830846</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:12">
+      <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>80731.20184965261</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>1324.399052494627</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>0.01640504565955903</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>0.983594954340441</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>11.54719032978368</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114">
         <v>5081.225793667651</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114">
         <v>52981.10309504155</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114">
         <v>352647.5612412376</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114">
         <v>81.32462551380182</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114">
         <v>3789.003766959325</v>
       </c>
-      <c r="L114" t="n">
+      <c r="L114">
         <v>44379.9430647675</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:12">
+      <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>79406.80279715799</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>1416.75354758196</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>0.01784171503795473</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>0.9821582849620453</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>10.73144265943442</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115">
         <v>4875.968831722932</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115">
         <v>47899.8773013739</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115">
         <v>299666.458146196</v>
       </c>
-      <c r="J115" t="n">
+      <c r="J115">
         <v>84.87380139468254</v>
       </c>
-      <c r="K115" t="n">
+      <c r="K115">
         <v>3707.679141445523</v>
       </c>
-      <c r="L115" t="n">
+      <c r="L115">
         <v>40590.93929780817</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:12">
+      <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>77990.04924957603</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>1513.419876297828</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>0.01940529453257211</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>0.9805947054674279</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>9.917305251189534</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116">
         <v>4672.168961261837</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116">
         <v>43023.90846965097</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I116">
         <v>251766.5808448222</v>
       </c>
-      <c r="J116" t="n">
+      <c r="J116">
         <v>88.45347785290484</v>
       </c>
-      <c r="K116" t="n">
+      <c r="K116">
         <v>3622.805340050841</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L116">
         <v>36883.26015636265</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:12">
+      <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>76476.62937327819</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>1614.173938472536</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>0.02110676100268283</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>0.9788932389973172</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>9.103667242625498</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117">
         <v>4469.760142890351</v>
       </c>
-      <c r="H117" t="n">
+      <c r="H117">
         <v>38351.73950838913</v>
       </c>
-      <c r="I117" t="n">
+      <c r="I117">
         <v>208742.6723751712</v>
       </c>
-      <c r="J117" t="n">
+      <c r="J117">
         <v>92.04113080517472</v>
       </c>
-      <c r="K117" t="n">
+      <c r="K117">
         <v>3534.351862197936</v>
       </c>
-      <c r="L117" t="n">
+      <c r="L117">
         <v>33260.45481631181</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:12">
+      <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>74862.45543480566</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>1718.692015156838</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>0.02295799683799538</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>0.9770420031620046</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>8.289178329026214</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118">
         <v>4268.70047201468</v>
       </c>
-      <c r="H118" t="n">
+      <c r="H118">
         <v>33881.97936549879</v>
       </c>
-      <c r="I118" t="n">
+      <c r="I118">
         <v>170390.9328667821</v>
       </c>
-      <c r="J118" t="n">
+      <c r="J118">
         <v>95.61054823303648</v>
       </c>
-      <c r="K118" t="n">
+      <c r="K118">
         <v>3442.310731392761</v>
       </c>
-      <c r="L118" t="n">
+      <c r="L118">
         <v>29726.10295411387</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:12">
+      <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>73143.76341964882</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>1826.535552792974</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>0.02497185634698018</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>0.9750281436530198</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>7.472204167086028</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G119">
         <v>4068.975278122749</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H119">
         <v>29613.2788934841</v>
       </c>
-      <c r="I119" t="n">
+      <c r="I119">
         <v>136508.9535012833</v>
       </c>
-      <c r="J119" t="n">
+      <c r="J119">
         <v>99.13157670701953</v>
       </c>
-      <c r="K119" t="n">
+      <c r="K119">
         <v>3346.700183159724</v>
       </c>
-      <c r="L119" t="n">
+      <c r="L119">
         <v>26283.79222272111</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
+    <row r="120" spans="1:12">
+      <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>71317.22786685584</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120">
         <v>1937.135330736752</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>0.02716223539077045</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>0.9728377646092295</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>6.650772223829473</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120">
         <v>3870.600401949321</v>
       </c>
-      <c r="H120" t="n">
+      <c r="H120">
         <v>25544.30361536136</v>
       </c>
-      <c r="I120" t="n">
+      <c r="I120">
         <v>106895.6746077992</v>
       </c>
-      <c r="J120" t="n">
+      <c r="J120">
         <v>102.5699114354714</v>
       </c>
-      <c r="K120" t="n">
+      <c r="K120">
         <v>3247.568606452705</v>
       </c>
-      <c r="L120" t="n">
+      <c r="L120">
         <v>22937.09203956139</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:12">
+      <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>69380.09253611909</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121">
         <v>2049.775449749399</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>0.02954414407392569</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>0.9704558559260743</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>5.822505609452899</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121">
         <v>3673.625602661428</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H121">
         <v>21673.70321341203</v>
       </c>
-      <c r="I121" t="n">
+      <c r="I121">
         <v>81351.37099243781</v>
       </c>
-      <c r="J121" t="n">
+      <c r="J121">
         <v>105.8869503206745</v>
       </c>
-      <c r="K121" t="n">
+      <c r="K121">
         <v>3144.998695017233</v>
       </c>
-      <c r="L121" t="n">
+      <c r="L121">
         <v>19689.52343310868</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:12">
+      <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>67330.31708636969</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122">
         <v>2163.577745065186</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>0.03213378220527019</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>0.9678662177947298</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>4.984541699605498</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122">
         <v>3478.138027885597</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H122">
         <v>18000.07761075061</v>
       </c>
-      <c r="I122" t="n">
+      <c r="I122">
         <v>59677.66777902578</v>
       </c>
-      <c r="J122" t="n">
+      <c r="J122">
         <v>109.0397364565305</v>
       </c>
-      <c r="K122" t="n">
+      <c r="K122">
         <v>3039.111744696559</v>
       </c>
-      <c r="L122" t="n">
+      <c r="L122">
         <v>16544.52473809144</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:12">
+      <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>65166.7393413045</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123">
         <v>2277.487422360631</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>0.0349486171224942</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>0.9650513828775058</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>4.133431374248671</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G123">
         <v>3284.265656602588</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H123">
         <v>14521.93958286501</v>
       </c>
-      <c r="I123" t="n">
+      <c r="I123">
         <v>41677.59016827517</v>
       </c>
-      <c r="J123" t="n">
+      <c r="J123">
         <v>111.9810175230838</v>
       </c>
-      <c r="K123" t="n">
+      <c r="K123">
         <v>2930.072008240028</v>
       </c>
-      <c r="L123" t="n">
+      <c r="L123">
         <v>13505.41299339489</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:12">
+      <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>62889.25191894387</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124">
         <v>2390.26093614141</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>0.03800746332969818</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>0.9619925366703018</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>3.265013385520285</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G124">
         <v>3092.180598674563</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H124">
         <v>11237.67392626242</v>
       </c>
-      <c r="I124" t="n">
+      <c r="I124">
         <v>27155.65058541016</v>
       </c>
-      <c r="J124" t="n">
+      <c r="J124">
         <v>114.6594543540757</v>
       </c>
-      <c r="K124" t="n">
+      <c r="K124">
         <v>2818.090990716945</v>
       </c>
-      <c r="L124" t="n">
+      <c r="L124">
         <v>10575.34098515486</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:12">
+      <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>60498.99098280246</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125">
         <v>2500.457371775463</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>0.04133056322354611</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>0.9586694367764539</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>2.374256587364691</v>
       </c>
-      <c r="G125" t="n">
+      <c r="G125">
         <v>2902.102105328426</v>
       </c>
-      <c r="H125" t="n">
+      <c r="H125">
         <v>8145.493327587858</v>
       </c>
-      <c r="I125" t="n">
+      <c r="I125">
         <v>15917.97665914773</v>
       </c>
-      <c r="J125" t="n">
+      <c r="J125">
         <v>117.0200141906954</v>
       </c>
-      <c r="K125" t="n">
+      <c r="K125">
         <v>2703.431536362869</v>
       </c>
-      <c r="L125" t="n">
+      <c r="L125">
         <v>7757.249994437914</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:12">
+      <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>57998.533611027</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126">
         <v>2606.434843619421</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>0.04493966797677573</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>0.9550603320232243</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>1.455060332023224</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G126">
         <v>2714.299112958989</v>
       </c>
-      <c r="H126" t="n">
+      <c r="H126">
         <v>5243.391222259434</v>
       </c>
-      <c r="I126" t="n">
+      <c r="I126">
         <v>7772.483331559878</v>
       </c>
-      <c r="J126" t="n">
+      <c r="J126">
         <v>119.0045862693013</v>
       </c>
-      <c r="K126" t="n">
+      <c r="K126">
         <v>2586.411522172174</v>
       </c>
-      <c r="L126" t="n">
+      <c r="L126">
         <v>5053.818458075046</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:12">
+      <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>55392.09876740758</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127">
         <v>55392.09876740758</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>1</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>0</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>0.5</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127">
         <v>2529.092109300444</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127">
         <v>2529.092109300444</v>
       </c>
-      <c r="I127" t="n">
+      <c r="I127">
         <v>2529.092109300444</v>
       </c>
-      <c r="J127" t="n">
+      <c r="J127">
         <v>2467.406935902872</v>
       </c>
-      <c r="K127" t="n">
+      <c r="K127">
         <v>2467.406935902872</v>
       </c>
-      <c r="L127" t="n">
+      <c r="L127">
         <v>2467.406935902872</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>